--- a/artfynd/A 33463-2026 artfynd.xlsx
+++ b/artfynd/A 33463-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56091554</v>
+        <v>136693770</v>
       </c>
       <c r="B2" t="n">
-        <v>109815</v>
+        <v>92105</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,46 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220204</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bunkängarnaområdet, Upl</t>
+          <t>Bunken, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>641391</v>
+        <v>641271</v>
       </c>
       <c r="R2" t="n">
-        <v>6718080</v>
+        <v>6718529</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -739,7 +730,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Älvkarleby</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -749,17 +740,27 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Västland</t>
+          <t>Älvkarleby</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-07-14</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-07-14</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,74 +775,65 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/56091554</t>
+          <t>https://artportalen.se/Sighting/136693770</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>56091559</v>
+        <v>136693752</v>
       </c>
       <c r="B3" t="n">
-        <v>109815</v>
+        <v>96557</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220204</v>
+        <v>2812</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hällskär, Upl</t>
+          <t>Bunken, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>641409</v>
+        <v>641362</v>
       </c>
       <c r="R3" t="n">
-        <v>6718489</v>
+        <v>6718541</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,7 +842,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Älvkarleby</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -860,17 +852,27 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Västland</t>
+          <t>Älvkarleby</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-07-15</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-07-15</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,70 +887,65 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/56091559</t>
+          <t>https://artportalen.se/Sighting/136693752</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>81678907</v>
+        <v>136693800</v>
       </c>
       <c r="B4" t="n">
-        <v>106414</v>
+        <v>96557</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221447</v>
+        <v>2812</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>590</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Hylocomiadelphus triquetrus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>vägkant 1 km NNO Bunken, Upl</t>
+          <t>Bunken, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>641394</v>
+        <v>641195</v>
       </c>
       <c r="R4" t="n">
-        <v>6718669</v>
+        <v>6718476</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,17 +969,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-08-14</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-08-14</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>sen?, Ebbe Z räknade mer exakt, 571 ex fanns i södra vägkanten</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,77 +999,65 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tommy Löfgren, Ebbe Zachrisson, Maria Forslund</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/81678907</t>
+          <t>https://artportalen.se/Sighting/136693800</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102656460</v>
+        <v>136693803</v>
       </c>
       <c r="B5" t="n">
-        <v>106414</v>
+        <v>87483</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221447</v>
+        <v>3674</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bunken, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>641421</v>
+        <v>641196</v>
       </c>
       <c r="R5" t="n">
-        <v>6718131</v>
+        <v>6718481</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1076,7 +1066,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Älvkarleby</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1086,22 +1076,27 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Västland</t>
+          <t>Älvkarleby</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Intermediär. 4 ledstycken. Tillsammans med krissla, väddklint, slåtterfibbla.</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,93 +1105,71 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>ÅGP Fältgentiana C-län</t>
-        </is>
-      </c>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102656460</t>
+          <t>https://artportalen.se/Sighting/136693803</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102656489</v>
+        <v>136693766</v>
       </c>
       <c r="B6" t="n">
-        <v>106414</v>
+        <v>4777</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221447</v>
+        <v>100299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bunken, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>641371</v>
+        <v>641359</v>
       </c>
       <c r="R6" t="n">
-        <v>6718072</v>
+        <v>6718519</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1220,17 +1193,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Intermediär</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,86 +1221,68 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
-      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>ÅGP Fältgentiana C-län</t>
-        </is>
-      </c>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102656489</t>
+          <t>https://artportalen.se/Sighting/136693766</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>56091868</v>
+        <v>136693772</v>
       </c>
       <c r="B7" t="n">
-        <v>106417</v>
+        <v>5182</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>224210</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tidig fältgentiana</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gentianella campestris var. suecica</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Froel.) Dostál</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bunkängarnaområdet, Upl</t>
+          <t>Bunken, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>641405</v>
+        <v>641271</v>
       </c>
       <c r="R7" t="n">
-        <v>6718135</v>
+        <v>6718529</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1331,7 +1291,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Älvkarleby</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1341,17 +1301,27 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Västland</t>
+          <t>Älvkarleby</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2015-07-14</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2015-07-14</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,74 +1336,65 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/56091868</t>
+          <t>https://artportalen.se/Sighting/136693772</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>88866193</v>
+        <v>136693748</v>
       </c>
       <c r="B8" t="n">
-        <v>106417</v>
+        <v>99323</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>224210</v>
+        <v>219798</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tidig fältgentiana</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gentianella campestris var. suecica</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Froel.) Dostál</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Väg vid Bunkängarna, Upl</t>
+          <t>Bunken, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>641426</v>
+        <v>641362</v>
       </c>
       <c r="R8" t="n">
-        <v>6718155</v>
+        <v>6718541</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1442,7 +1403,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Älvkarleby</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1452,22 +1413,27 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Västland</t>
+          <t>Älvkarleby</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2020-07-16</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2020-07-16</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>200m vägsträcka</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,22 +1448,1850 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136693748</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136693805</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99323</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bunken, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>641181</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6718500</v>
+      </c>
+      <c r="S9" t="n">
+        <v>7</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136693805</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>56091554</v>
+      </c>
+      <c r="B10" t="n">
+        <v>109815</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bunkängarnaområdet, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>641391</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6718080</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Västland</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2015-07-14</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2015-07-14</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Tommy Löfgren</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Tommy Löfgren</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr">
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091554</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>56091559</v>
+      </c>
+      <c r="B11" t="n">
+        <v>109815</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hällskär, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>641409</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6718489</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Västland</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2015-07-15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2015-07-15</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091559</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136693744</v>
+      </c>
+      <c r="B12" t="n">
+        <v>102471</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bunken, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>641378</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6718554</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136693744</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136693746</v>
+      </c>
+      <c r="B13" t="n">
+        <v>102471</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bunken, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>641380</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6718544</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Västland</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136693746</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136693757</v>
+      </c>
+      <c r="B14" t="n">
+        <v>102471</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bunken, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>641368</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6718544</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Västland</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136693757</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136693781</v>
+      </c>
+      <c r="B15" t="n">
+        <v>102471</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bunken, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>641330</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6718613</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136693781</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>81678907</v>
+      </c>
+      <c r="B16" t="n">
+        <v>106414</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221447</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Fältgentiana</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>vägkant 1 km NNO Bunken, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>641394</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6718669</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2019-08-14</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2019-08-14</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>sen?, Ebbe Z räknade mer exakt, 571 ex fanns i södra vägkanten</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren, Ebbe Zachrisson, Maria Forslund</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81678907</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>102656460</v>
+      </c>
+      <c r="B17" t="n">
+        <v>106414</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221447</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Fältgentiana</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bunken, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>641421</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6718131</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Västland</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2022-08-01</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2022-08-01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Intermediär. 4 ledstycken. Tillsammans med krissla, väddklint, slåtterfibbla.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
         <is>
           <t>ÅGP Fältgentiana C-län</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102656460</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>102656489</v>
+      </c>
+      <c r="B18" t="n">
+        <v>106414</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221447</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Fältgentiana</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bunken, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>641371</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6718072</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Västland</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2022-08-01</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2022-08-01</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Intermediär</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>ÅGP Fältgentiana C-län</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102656489</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136693779</v>
+      </c>
+      <c r="B19" t="n">
+        <v>104868</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Bunken, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>641319</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6718604</v>
+      </c>
+      <c r="S19" t="n">
+        <v>8</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136693779</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136693750</v>
+      </c>
+      <c r="B20" t="n">
+        <v>101555</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Bunken, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>641362</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6718541</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136693750</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136693759</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99151</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Bunken, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>641367</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6718530</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Västland</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136693759</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>56091868</v>
+      </c>
+      <c r="B22" t="n">
+        <v>106417</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>224210</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tidig fältgentiana</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Gentianella campestris var. suecica</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Froel.) Dostál</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Bunkängarnaområdet, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>641405</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6718135</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Västland</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2015-07-14</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2015-07-14</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091868</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>88866193</v>
+      </c>
+      <c r="B23" t="n">
+        <v>106417</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>224210</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tidig fältgentiana</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Gentianella campestris var. suecica</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Froel.) Dostál</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Väg vid Bunkängarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>641426</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6718155</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Västland</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2020-07-16</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2020-07-16</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>200m vägsträcka</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>ÅGP Fältgentiana C-län</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/88866193</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136693783</v>
+      </c>
+      <c r="B24" t="n">
+        <v>87520</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Bunken, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>641320</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6718602</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136693783</t>
         </is>
       </c>
     </row>
@@ -1510,6 +3304,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33463-2026 artfynd.xlsx
+++ b/artfynd/A 33463-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136693770</v>
       </c>
       <c r="B2" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136693752</v>
       </c>
       <c r="B3" t="n">
-        <v>96557</v>
+        <v>96558</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136693800</v>
       </c>
       <c r="B4" t="n">
-        <v>96557</v>
+        <v>96558</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136693748</v>
       </c>
       <c r="B8" t="n">
-        <v>99323</v>
+        <v>99324</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136693805</v>
       </c>
       <c r="B9" t="n">
-        <v>99323</v>
+        <v>99324</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>136693744</v>
       </c>
       <c r="B12" t="n">
-        <v>102471</v>
+        <v>102472</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>136693746</v>
       </c>
       <c r="B13" t="n">
-        <v>102471</v>
+        <v>102472</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>136693757</v>
       </c>
       <c r="B14" t="n">
-        <v>102471</v>
+        <v>102472</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>136693781</v>
       </c>
       <c r="B15" t="n">
-        <v>102471</v>
+        <v>102472</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>136693779</v>
       </c>
       <c r="B19" t="n">
-        <v>104868</v>
+        <v>104869</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>136693750</v>
       </c>
       <c r="B20" t="n">
-        <v>101555</v>
+        <v>101556</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>136693759</v>
       </c>
       <c r="B21" t="n">
-        <v>99151</v>
+        <v>99152</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>641320</v>
       </c>
       <c r="R24" t="n">
-        <v>6718602</v>
+        <v>6718601</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>

--- a/artfynd/A 33463-2026 artfynd.xlsx
+++ b/artfynd/A 33463-2026 artfynd.xlsx
@@ -3222,7 +3222,7 @@
         <v>641320</v>
       </c>
       <c r="R24" t="n">
-        <v>6718601</v>
+        <v>6718602</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>

--- a/artfynd/A 33463-2026 artfynd.xlsx
+++ b/artfynd/A 33463-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136693770</v>
       </c>
       <c r="B2" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136693752</v>
       </c>
       <c r="B3" t="n">
-        <v>96558</v>
+        <v>96563</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136693800</v>
       </c>
       <c r="B4" t="n">
-        <v>96558</v>
+        <v>96563</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136693803</v>
       </c>
       <c r="B5" t="n">
-        <v>87483</v>
+        <v>87485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136693748</v>
       </c>
       <c r="B8" t="n">
-        <v>99324</v>
+        <v>99329</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136693805</v>
       </c>
       <c r="B9" t="n">
-        <v>99324</v>
+        <v>99329</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>136693744</v>
       </c>
       <c r="B12" t="n">
-        <v>102472</v>
+        <v>102477</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>136693746</v>
       </c>
       <c r="B13" t="n">
-        <v>102472</v>
+        <v>102477</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>136693757</v>
       </c>
       <c r="B14" t="n">
-        <v>102472</v>
+        <v>102477</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>136693781</v>
       </c>
       <c r="B15" t="n">
-        <v>102472</v>
+        <v>102477</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>136693779</v>
       </c>
       <c r="B19" t="n">
-        <v>104869</v>
+        <v>104874</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>136693750</v>
       </c>
       <c r="B20" t="n">
-        <v>101556</v>
+        <v>101561</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>136693759</v>
       </c>
       <c r="B21" t="n">
-        <v>99152</v>
+        <v>99157</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>136693783</v>
       </c>
       <c r="B24" t="n">
-        <v>87520</v>
+        <v>87522</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 33463-2026 artfynd.xlsx
+++ b/artfynd/A 33463-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136693770</v>
       </c>
       <c r="B2" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136693752</v>
       </c>
       <c r="B3" t="n">
-        <v>96563</v>
+        <v>96565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136693800</v>
       </c>
       <c r="B4" t="n">
-        <v>96563</v>
+        <v>96565</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136693803</v>
       </c>
       <c r="B5" t="n">
-        <v>87485</v>
+        <v>87487</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136693748</v>
       </c>
       <c r="B8" t="n">
-        <v>99329</v>
+        <v>99331</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136693805</v>
       </c>
       <c r="B9" t="n">
-        <v>99329</v>
+        <v>99331</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>136693744</v>
       </c>
       <c r="B12" t="n">
-        <v>102477</v>
+        <v>102479</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>136693746</v>
       </c>
       <c r="B13" t="n">
-        <v>102477</v>
+        <v>102479</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>136693757</v>
       </c>
       <c r="B14" t="n">
-        <v>102477</v>
+        <v>102479</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>136693781</v>
       </c>
       <c r="B15" t="n">
-        <v>102477</v>
+        <v>102479</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>136693779</v>
       </c>
       <c r="B19" t="n">
-        <v>104874</v>
+        <v>104876</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>136693750</v>
       </c>
       <c r="B20" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>136693759</v>
       </c>
       <c r="B21" t="n">
-        <v>99157</v>
+        <v>99159</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>136693783</v>
       </c>
       <c r="B24" t="n">
-        <v>87522</v>
+        <v>87524</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>641320</v>
       </c>
       <c r="R24" t="n">
-        <v>6718602</v>
+        <v>6718601</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>

--- a/artfynd/A 33463-2026 artfynd.xlsx
+++ b/artfynd/A 33463-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136693770</v>
       </c>
       <c r="B2" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136693752</v>
       </c>
       <c r="B3" t="n">
-        <v>96565</v>
+        <v>96571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136693800</v>
       </c>
       <c r="B4" t="n">
-        <v>96565</v>
+        <v>96571</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136693803</v>
       </c>
       <c r="B5" t="n">
-        <v>87487</v>
+        <v>87489</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136693748</v>
       </c>
       <c r="B8" t="n">
-        <v>99331</v>
+        <v>99337</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136693805</v>
       </c>
       <c r="B9" t="n">
-        <v>99331</v>
+        <v>99337</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>136693744</v>
       </c>
       <c r="B12" t="n">
-        <v>102479</v>
+        <v>102485</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>136693746</v>
       </c>
       <c r="B13" t="n">
-        <v>102479</v>
+        <v>102485</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>136693757</v>
       </c>
       <c r="B14" t="n">
-        <v>102479</v>
+        <v>102485</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>136693781</v>
       </c>
       <c r="B15" t="n">
-        <v>102479</v>
+        <v>102485</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>136693779</v>
       </c>
       <c r="B19" t="n">
-        <v>104876</v>
+        <v>104882</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>136693750</v>
       </c>
       <c r="B20" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>136693759</v>
       </c>
       <c r="B21" t="n">
-        <v>99159</v>
+        <v>99165</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>136693783</v>
       </c>
       <c r="B24" t="n">
-        <v>87524</v>
+        <v>87526</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 33463-2026 artfynd.xlsx
+++ b/artfynd/A 33463-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136693770</v>
       </c>
       <c r="B2" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136693752</v>
       </c>
       <c r="B3" t="n">
-        <v>96571</v>
+        <v>96573</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136693800</v>
       </c>
       <c r="B4" t="n">
-        <v>96571</v>
+        <v>96573</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136693803</v>
       </c>
       <c r="B5" t="n">
-        <v>87489</v>
+        <v>87491</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136693748</v>
       </c>
       <c r="B8" t="n">
-        <v>99337</v>
+        <v>99339</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136693805</v>
       </c>
       <c r="B9" t="n">
-        <v>99337</v>
+        <v>99339</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>136693744</v>
       </c>
       <c r="B12" t="n">
-        <v>102485</v>
+        <v>102487</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>136693746</v>
       </c>
       <c r="B13" t="n">
-        <v>102485</v>
+        <v>102487</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>136693757</v>
       </c>
       <c r="B14" t="n">
-        <v>102485</v>
+        <v>102487</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>136693781</v>
       </c>
       <c r="B15" t="n">
-        <v>102485</v>
+        <v>102487</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>136693779</v>
       </c>
       <c r="B19" t="n">
-        <v>104882</v>
+        <v>104884</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>136693750</v>
       </c>
       <c r="B20" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>136693759</v>
       </c>
       <c r="B21" t="n">
-        <v>99165</v>
+        <v>99167</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>136693783</v>
       </c>
       <c r="B24" t="n">
-        <v>87526</v>
+        <v>87528</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 33463-2026 artfynd.xlsx
+++ b/artfynd/A 33463-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136693770</v>
       </c>
       <c r="B2" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136693752</v>
       </c>
       <c r="B3" t="n">
-        <v>96573</v>
+        <v>96574</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136693800</v>
       </c>
       <c r="B4" t="n">
-        <v>96573</v>
+        <v>96574</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136693803</v>
       </c>
       <c r="B5" t="n">
-        <v>87491</v>
+        <v>87492</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136693748</v>
       </c>
       <c r="B8" t="n">
-        <v>99339</v>
+        <v>99340</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136693805</v>
       </c>
       <c r="B9" t="n">
-        <v>99339</v>
+        <v>99340</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>136693744</v>
       </c>
       <c r="B12" t="n">
-        <v>102487</v>
+        <v>102488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>136693746</v>
       </c>
       <c r="B13" t="n">
-        <v>102487</v>
+        <v>102488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>136693757</v>
       </c>
       <c r="B14" t="n">
-        <v>102487</v>
+        <v>102488</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>136693781</v>
       </c>
       <c r="B15" t="n">
-        <v>102487</v>
+        <v>102488</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>136693779</v>
       </c>
       <c r="B19" t="n">
-        <v>104884</v>
+        <v>104885</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>136693750</v>
       </c>
       <c r="B20" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>136693759</v>
       </c>
       <c r="B21" t="n">
-        <v>99167</v>
+        <v>99168</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>136693783</v>
       </c>
       <c r="B24" t="n">
-        <v>87528</v>
+        <v>87529</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 33463-2026 artfynd.xlsx
+++ b/artfynd/A 33463-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136693770</v>
       </c>
       <c r="B2" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136693752</v>
       </c>
       <c r="B3" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136693800</v>
       </c>
       <c r="B4" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136693803</v>
       </c>
       <c r="B5" t="n">
-        <v>87492</v>
+        <v>87498</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136693748</v>
       </c>
       <c r="B8" t="n">
-        <v>99340</v>
+        <v>99346</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136693805</v>
       </c>
       <c r="B9" t="n">
-        <v>99340</v>
+        <v>99346</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>136693744</v>
       </c>
       <c r="B12" t="n">
-        <v>102488</v>
+        <v>102494</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>136693746</v>
       </c>
       <c r="B13" t="n">
-        <v>102488</v>
+        <v>102494</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>136693757</v>
       </c>
       <c r="B14" t="n">
-        <v>102488</v>
+        <v>102494</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>136693781</v>
       </c>
       <c r="B15" t="n">
-        <v>102488</v>
+        <v>102494</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>136693779</v>
       </c>
       <c r="B19" t="n">
-        <v>104885</v>
+        <v>104891</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>136693750</v>
       </c>
       <c r="B20" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>136693759</v>
       </c>
       <c r="B21" t="n">
-        <v>99168</v>
+        <v>99174</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>136693783</v>
       </c>
       <c r="B24" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>641320</v>
       </c>
       <c r="R24" t="n">
-        <v>6718602</v>
+        <v>6718601</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>

--- a/artfynd/A 33463-2026 artfynd.xlsx
+++ b/artfynd/A 33463-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136693770</v>
       </c>
       <c r="B2" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136693752</v>
       </c>
       <c r="B3" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136693800</v>
       </c>
       <c r="B4" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136693803</v>
       </c>
       <c r="B5" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136693748</v>
       </c>
       <c r="B8" t="n">
-        <v>99346</v>
+        <v>99350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136693805</v>
       </c>
       <c r="B9" t="n">
-        <v>99346</v>
+        <v>99350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>136693744</v>
       </c>
       <c r="B12" t="n">
-        <v>102494</v>
+        <v>102498</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>136693746</v>
       </c>
       <c r="B13" t="n">
-        <v>102494</v>
+        <v>102498</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>136693757</v>
       </c>
       <c r="B14" t="n">
-        <v>102494</v>
+        <v>102498</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>136693781</v>
       </c>
       <c r="B15" t="n">
-        <v>102494</v>
+        <v>102498</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>136693779</v>
       </c>
       <c r="B19" t="n">
-        <v>104891</v>
+        <v>104895</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>136693750</v>
       </c>
       <c r="B20" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>136693759</v>
       </c>
       <c r="B21" t="n">
-        <v>99174</v>
+        <v>99178</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>136693783</v>
       </c>
       <c r="B24" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>641320</v>
       </c>
       <c r="R24" t="n">
-        <v>6718601</v>
+        <v>6718602</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>

--- a/artfynd/A 33463-2026 artfynd.xlsx
+++ b/artfynd/A 33463-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136693752</v>
       </c>
       <c r="B3" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136693800</v>
       </c>
       <c r="B4" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136693748</v>
       </c>
       <c r="B8" t="n">
-        <v>99350</v>
+        <v>99352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136693805</v>
       </c>
       <c r="B9" t="n">
-        <v>99350</v>
+        <v>99352</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>136693744</v>
       </c>
       <c r="B12" t="n">
-        <v>102498</v>
+        <v>102500</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>136693746</v>
       </c>
       <c r="B13" t="n">
-        <v>102498</v>
+        <v>102500</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>136693757</v>
       </c>
       <c r="B14" t="n">
-        <v>102498</v>
+        <v>102500</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>136693781</v>
       </c>
       <c r="B15" t="n">
-        <v>102498</v>
+        <v>102500</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>136693779</v>
       </c>
       <c r="B19" t="n">
-        <v>104895</v>
+        <v>104897</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>136693750</v>
       </c>
       <c r="B20" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>136693759</v>
       </c>
       <c r="B21" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 33463-2026 artfynd.xlsx
+++ b/artfynd/A 33463-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136693770</v>
       </c>
       <c r="B2" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136693752</v>
       </c>
       <c r="B3" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136693800</v>
       </c>
       <c r="B4" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136693803</v>
       </c>
       <c r="B5" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136693748</v>
       </c>
       <c r="B8" t="n">
-        <v>99352</v>
+        <v>99354</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136693805</v>
       </c>
       <c r="B9" t="n">
-        <v>99352</v>
+        <v>99354</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>136693744</v>
       </c>
       <c r="B12" t="n">
-        <v>102500</v>
+        <v>102502</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>136693746</v>
       </c>
       <c r="B13" t="n">
-        <v>102500</v>
+        <v>102502</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>136693757</v>
       </c>
       <c r="B14" t="n">
-        <v>102500</v>
+        <v>102502</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>136693781</v>
       </c>
       <c r="B15" t="n">
-        <v>102500</v>
+        <v>102502</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>136693779</v>
       </c>
       <c r="B19" t="n">
-        <v>104897</v>
+        <v>104899</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>136693750</v>
       </c>
       <c r="B20" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>136693759</v>
       </c>
       <c r="B21" t="n">
-        <v>99180</v>
+        <v>99182</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>136693783</v>
       </c>
       <c r="B24" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 33463-2026 artfynd.xlsx
+++ b/artfynd/A 33463-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136693770</v>
       </c>
       <c r="B2" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136693752</v>
       </c>
       <c r="B3" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136693800</v>
       </c>
       <c r="B4" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136693803</v>
       </c>
       <c r="B5" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136693748</v>
       </c>
       <c r="B8" t="n">
-        <v>99354</v>
+        <v>99367</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136693805</v>
       </c>
       <c r="B9" t="n">
-        <v>99354</v>
+        <v>99367</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>136693744</v>
       </c>
       <c r="B12" t="n">
-        <v>102502</v>
+        <v>102515</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>136693746</v>
       </c>
       <c r="B13" t="n">
-        <v>102502</v>
+        <v>102515</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>136693757</v>
       </c>
       <c r="B14" t="n">
-        <v>102502</v>
+        <v>102515</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>136693781</v>
       </c>
       <c r="B15" t="n">
-        <v>102502</v>
+        <v>102515</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>136693779</v>
       </c>
       <c r="B19" t="n">
-        <v>104899</v>
+        <v>104912</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>136693750</v>
       </c>
       <c r="B20" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>136693759</v>
       </c>
       <c r="B21" t="n">
-        <v>99182</v>
+        <v>99195</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>136693783</v>
       </c>
       <c r="B24" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 33463-2026 artfynd.xlsx
+++ b/artfynd/A 33463-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136693770</v>
       </c>
       <c r="B2" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136693752</v>
       </c>
       <c r="B3" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136693800</v>
       </c>
       <c r="B4" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136693803</v>
       </c>
       <c r="B5" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136693748</v>
       </c>
       <c r="B8" t="n">
-        <v>99367</v>
+        <v>99369</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136693805</v>
       </c>
       <c r="B9" t="n">
-        <v>99367</v>
+        <v>99369</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>136693744</v>
       </c>
       <c r="B12" t="n">
-        <v>102515</v>
+        <v>102517</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>136693746</v>
       </c>
       <c r="B13" t="n">
-        <v>102515</v>
+        <v>102517</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>136693757</v>
       </c>
       <c r="B14" t="n">
-        <v>102515</v>
+        <v>102517</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>136693781</v>
       </c>
       <c r="B15" t="n">
-        <v>102515</v>
+        <v>102517</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>136693779</v>
       </c>
       <c r="B19" t="n">
-        <v>104912</v>
+        <v>104914</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>136693750</v>
       </c>
       <c r="B20" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>136693759</v>
       </c>
       <c r="B21" t="n">
-        <v>99195</v>
+        <v>99197</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>136693783</v>
       </c>
       <c r="B24" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>641320</v>
       </c>
       <c r="R24" t="n">
-        <v>6718602</v>
+        <v>6718601</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>

--- a/artfynd/A 33463-2026 artfynd.xlsx
+++ b/artfynd/A 33463-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136693770</v>
       </c>
       <c r="B2" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136693752</v>
       </c>
       <c r="B3" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136693800</v>
       </c>
       <c r="B4" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136693803</v>
       </c>
       <c r="B5" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136693748</v>
       </c>
       <c r="B8" t="n">
-        <v>99369</v>
+        <v>99372</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136693805</v>
       </c>
       <c r="B9" t="n">
-        <v>99369</v>
+        <v>99372</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>136693744</v>
       </c>
       <c r="B12" t="n">
-        <v>102517</v>
+        <v>102520</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>136693746</v>
       </c>
       <c r="B13" t="n">
-        <v>102517</v>
+        <v>102520</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>136693757</v>
       </c>
       <c r="B14" t="n">
-        <v>102517</v>
+        <v>102520</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>136693781</v>
       </c>
       <c r="B15" t="n">
-        <v>102517</v>
+        <v>102520</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>136693779</v>
       </c>
       <c r="B19" t="n">
-        <v>104914</v>
+        <v>104917</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>136693750</v>
       </c>
       <c r="B20" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>136693759</v>
       </c>
       <c r="B21" t="n">
-        <v>99197</v>
+        <v>99200</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>136693783</v>
       </c>
       <c r="B24" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>641320</v>
       </c>
       <c r="R24" t="n">
-        <v>6718601</v>
+        <v>6718602</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>

--- a/artfynd/A 33463-2026 artfynd.xlsx
+++ b/artfynd/A 33463-2026 artfynd.xlsx
@@ -3187,7 +3187,7 @@
         <v>136693783</v>
       </c>
       <c r="B24" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
